--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/131.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/131.xlsx
@@ -426,13 +426,13 @@
         <v>-18.6641726774098</v>
       </c>
       <c r="E2">
-        <v>-7.807467129273935</v>
+        <v>-17.8620787247705</v>
       </c>
       <c r="F2">
-        <v>-2.982158417124048</v>
+        <v>-5.304614827819896</v>
       </c>
       <c r="G2">
-        <v>-5.493493934170628</v>
+        <v>-12.60869386608584</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.87799692251233</v>
       </c>
       <c r="E3">
-        <v>-6.991997643868688</v>
+        <v>-18.98300736741513</v>
       </c>
       <c r="F3">
-        <v>-2.495708771871469</v>
+        <v>-5.223509375411797</v>
       </c>
       <c r="G3">
-        <v>-5.354633101525898</v>
+        <v>-12.98148777817209</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.04623103639633</v>
       </c>
       <c r="E4">
-        <v>-9.26804490791587</v>
+        <v>-19.44310032659444</v>
       </c>
       <c r="F4">
-        <v>-3.346257368615738</v>
+        <v>-5.077782153543905</v>
       </c>
       <c r="G4">
-        <v>-4.882883672725293</v>
+        <v>-12.61002139484709</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.26576549574022</v>
       </c>
       <c r="E5">
-        <v>-8.775306179615267</v>
+        <v>-19.31019867141733</v>
       </c>
       <c r="F5">
-        <v>-2.670080938528168</v>
+        <v>-5.270579696341073</v>
       </c>
       <c r="G5">
-        <v>-4.397918546131917</v>
+        <v>-12.19707718646056</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.50127143659015</v>
       </c>
       <c r="E6">
-        <v>-10.10097618909469</v>
+        <v>-20.09300427380525</v>
       </c>
       <c r="F6">
-        <v>-3.211607904025483</v>
+        <v>-5.367260941024012</v>
       </c>
       <c r="G6">
-        <v>-3.628680184626864</v>
+        <v>-12.21939357394079</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.76016146490727</v>
       </c>
       <c r="E7">
-        <v>-11.39926251624974</v>
+        <v>-20.44713999815309</v>
       </c>
       <c r="F7">
-        <v>-3.41986278255889</v>
+        <v>-5.524533947752123</v>
       </c>
       <c r="G7">
-        <v>-3.022694755299891</v>
+        <v>-11.43362234801261</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.0230518393714</v>
       </c>
       <c r="E8">
-        <v>-11.68513149493195</v>
+        <v>-21.46136420775499</v>
       </c>
       <c r="F8">
-        <v>-3.487912336331467</v>
+        <v>-5.229244162941377</v>
       </c>
       <c r="G8">
-        <v>-2.138424867941782</v>
+        <v>-11.64243500790215</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.27081324688783</v>
       </c>
       <c r="E9">
-        <v>-11.86176915207514</v>
+        <v>-22.21404640104389</v>
       </c>
       <c r="F9">
-        <v>-3.796287012636833</v>
+        <v>-5.338259798252001</v>
       </c>
       <c r="G9">
-        <v>-2.626419143703591</v>
+        <v>-11.03902187245919</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.47465101313157</v>
       </c>
       <c r="E10">
-        <v>-12.74400645824948</v>
+        <v>-22.12526566812351</v>
       </c>
       <c r="F10">
-        <v>-3.654786949625427</v>
+        <v>-5.34267416814152</v>
       </c>
       <c r="G10">
-        <v>-2.670989018298799</v>
+        <v>-10.77515152970604</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.63665765376452</v>
       </c>
       <c r="E11">
-        <v>-12.92895386519674</v>
+        <v>-22.89971170749327</v>
       </c>
       <c r="F11">
-        <v>-3.990952523927314</v>
+        <v>-5.178327732160903</v>
       </c>
       <c r="G11">
-        <v>-1.968441596682364</v>
+        <v>-10.02119464641026</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.76847748459054</v>
       </c>
       <c r="E12">
-        <v>-15.01156283353228</v>
+        <v>-23.8641272314848</v>
       </c>
       <c r="F12">
-        <v>-3.365863168305196</v>
+        <v>-5.225317701452108</v>
       </c>
       <c r="G12">
-        <v>-0.4390291473587824</v>
+        <v>-10.05214493665691</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.89605892124337</v>
       </c>
       <c r="E13">
-        <v>-14.43259290317761</v>
+        <v>-23.92739907031998</v>
       </c>
       <c r="F13">
-        <v>-4.077989086939458</v>
+        <v>-5.350240475998691</v>
       </c>
       <c r="G13">
-        <v>-0.6918588207384622</v>
+        <v>-9.916541680822819</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.084585797438322</v>
       </c>
       <c r="E14">
-        <v>-16.4962773786351</v>
+        <v>-25.15054895673975</v>
       </c>
       <c r="F14">
-        <v>-3.857201837969098</v>
+        <v>-5.353250763140464</v>
       </c>
       <c r="G14">
-        <v>-1.156536924267184</v>
+        <v>-9.506209492866773</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.402034906324909</v>
       </c>
       <c r="E15">
-        <v>-16.0929261987719</v>
+        <v>-25.59416279900515</v>
       </c>
       <c r="F15">
-        <v>-3.597028204097829</v>
+        <v>-4.96098400648398</v>
       </c>
       <c r="G15">
-        <v>0.5167915607395948</v>
+        <v>-8.819307709468934</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.907076778578341</v>
       </c>
       <c r="E16">
-        <v>-18.18115500335095</v>
+        <v>-25.91761358347701</v>
       </c>
       <c r="F16">
-        <v>-3.302275201364098</v>
+        <v>-4.897768804874142</v>
       </c>
       <c r="G16">
-        <v>0.7259783122750625</v>
+        <v>-8.88473071041601</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.653357284512714</v>
       </c>
       <c r="E17">
-        <v>-18.59560547300695</v>
+        <v>-26.91942071734988</v>
       </c>
       <c r="F17">
-        <v>-3.755707778675894</v>
+        <v>-4.827878618732544</v>
       </c>
       <c r="G17">
-        <v>1.963791289408559</v>
+        <v>-8.412060949955489</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.677741044988673</v>
       </c>
       <c r="E18">
-        <v>-18.87474966778777</v>
+        <v>-26.92892598429198</v>
       </c>
       <c r="F18">
-        <v>-3.01433469215099</v>
+        <v>-4.521728937271098</v>
       </c>
       <c r="G18">
-        <v>1.845495565653782</v>
+        <v>-8.521623454577668</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.981275705489746</v>
       </c>
       <c r="E19">
-        <v>-20.59256741243542</v>
+        <v>-28.32380013355663</v>
       </c>
       <c r="F19">
-        <v>-2.915557677938968</v>
+        <v>-4.096759892286896</v>
       </c>
       <c r="G19">
-        <v>2.298219289240195</v>
+        <v>-8.129489335450996</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.53205482837201</v>
       </c>
       <c r="E20">
-        <v>-20.21948002436548</v>
+        <v>-28.54902831680212</v>
       </c>
       <c r="F20">
-        <v>-2.769787380966131</v>
+        <v>-4.212307204568592</v>
       </c>
       <c r="G20">
-        <v>1.774361873651462</v>
+        <v>-8.037956061835686</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.293657121246138</v>
       </c>
       <c r="E21">
-        <v>-21.25548166547027</v>
+        <v>-28.59880530309443</v>
       </c>
       <c r="F21">
-        <v>-2.47077656978201</v>
+        <v>-3.785108194536054</v>
       </c>
       <c r="G21">
-        <v>1.1097301300963</v>
+        <v>-8.588989745756297</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.20354992458326</v>
       </c>
       <c r="E22">
-        <v>-23.31053939794313</v>
+        <v>-29.96488967885531</v>
       </c>
       <c r="F22">
-        <v>-2.039879727663374</v>
+        <v>-3.7318897307432</v>
       </c>
       <c r="G22">
-        <v>2.276306788315759</v>
+        <v>-8.521179841475405</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-11.18098641390215</v>
       </c>
       <c r="E23">
-        <v>-22.023420287691</v>
+        <v>-30.30195079195723</v>
       </c>
       <c r="F23">
-        <v>-2.019496090982687</v>
+        <v>-3.488049016952929</v>
       </c>
       <c r="G23">
-        <v>1.820368525010714</v>
+        <v>-8.120302571579519</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-12.15521350874465</v>
       </c>
       <c r="E24">
-        <v>-21.90668528472128</v>
+        <v>-30.65355509933478</v>
       </c>
       <c r="F24">
-        <v>-1.793448709004549</v>
+        <v>-3.463930271653018</v>
       </c>
       <c r="G24">
-        <v>0.3977608958750992</v>
+        <v>-8.728986095520998</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-13.05393431807099</v>
       </c>
       <c r="E25">
-        <v>-21.78286321992955</v>
+        <v>-30.8848786085946</v>
       </c>
       <c r="F25">
-        <v>-2.001635661410927</v>
+        <v>-3.546467142933155</v>
       </c>
       <c r="G25">
-        <v>0.3188540429465705</v>
+        <v>-8.498817106357629</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-13.80983395443211</v>
       </c>
       <c r="E26">
-        <v>-24.06612434307095</v>
+        <v>-30.98000826207373</v>
       </c>
       <c r="F26">
-        <v>-1.80497129957749</v>
+        <v>-3.529836838954552</v>
       </c>
       <c r="G26">
-        <v>0.7541047071767105</v>
+        <v>-8.391283966151022</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-14.37716915482541</v>
       </c>
       <c r="E27">
-        <v>-23.27548448064976</v>
+        <v>-30.49165988932356</v>
       </c>
       <c r="F27">
-        <v>-1.876869448303474</v>
+        <v>-3.448532578369781</v>
       </c>
       <c r="G27">
-        <v>0.9135240276203145</v>
+        <v>-8.387271584957425</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-14.73722063394899</v>
       </c>
       <c r="E28">
-        <v>-22.12612607818497</v>
+        <v>-31.08298349677115</v>
       </c>
       <c r="F28">
-        <v>-1.682952781145123</v>
+        <v>-3.298510271518374</v>
       </c>
       <c r="G28">
-        <v>0.1987242769630369</v>
+        <v>-9.060235971634933</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-14.88789945368249</v>
       </c>
       <c r="E29">
-        <v>-23.42843821873283</v>
+        <v>-30.34335915828337</v>
       </c>
       <c r="F29">
-        <v>-1.645438506574542</v>
+        <v>-3.224575167348907</v>
       </c>
       <c r="G29">
-        <v>0.1275508584142457</v>
+        <v>-8.837088649560359</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-14.84277636897337</v>
       </c>
       <c r="E30">
-        <v>-22.86368316828825</v>
+        <v>-30.64676691679728</v>
       </c>
       <c r="F30">
-        <v>-1.511435168558472</v>
+        <v>-3.270329212475135</v>
       </c>
       <c r="G30">
-        <v>-0.07286625798769274</v>
+        <v>-8.91962054985439</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-14.64581365644229</v>
       </c>
       <c r="E31">
-        <v>-22.00880237359425</v>
+        <v>-30.04371909014384</v>
       </c>
       <c r="F31">
-        <v>-1.588565285800537</v>
+        <v>-3.099919127106026</v>
       </c>
       <c r="G31">
-        <v>0.06771605833745822</v>
+        <v>-9.052221140884358</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-14.34253137286544</v>
       </c>
       <c r="E32">
-        <v>-22.21168253761189</v>
+        <v>-29.75965697259069</v>
       </c>
       <c r="F32">
-        <v>-1.191589260459138</v>
+        <v>-3.196735395675621</v>
       </c>
       <c r="G32">
-        <v>0.4722150650533082</v>
+        <v>-8.900578291912502</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-13.97270480193431</v>
       </c>
       <c r="E33">
-        <v>-22.00445503854688</v>
+        <v>-29.75482509082451</v>
       </c>
       <c r="F33">
-        <v>-1.700493460899403</v>
+        <v>-3.415624854926168</v>
       </c>
       <c r="G33">
-        <v>-0.07499493876944412</v>
+        <v>-8.578217230571509</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-13.57961242200485</v>
       </c>
       <c r="E34">
-        <v>-21.23976786066365</v>
+        <v>-29.28096557066188</v>
       </c>
       <c r="F34">
-        <v>-1.682475641521111</v>
+        <v>-3.515274140013337</v>
       </c>
       <c r="G34">
-        <v>-0.8369567211791791</v>
+        <v>-8.877934160423887</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-13.1956818682453</v>
       </c>
       <c r="E35">
-        <v>-21.18427141169965</v>
+        <v>-28.55942116464972</v>
       </c>
       <c r="F35">
-        <v>-1.325634845212751</v>
+        <v>-3.322949595003168</v>
       </c>
       <c r="G35">
-        <v>-0.003897662768056101</v>
+        <v>-8.698294027826414</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-12.83436730811602</v>
       </c>
       <c r="E36">
-        <v>-20.99599104788274</v>
+        <v>-29.14190519083434</v>
       </c>
       <c r="F36">
-        <v>-1.34736540729039</v>
+        <v>-3.191575495123583</v>
       </c>
       <c r="G36">
-        <v>-0.4972682644856411</v>
+        <v>-9.022902949588572</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-12.49810605445729</v>
       </c>
       <c r="E37">
-        <v>-21.68129860488552</v>
+        <v>-28.71996009669564</v>
       </c>
       <c r="F37">
-        <v>-1.626214584257774</v>
+        <v>-3.237917681105798</v>
       </c>
       <c r="G37">
-        <v>0.6978188119180218</v>
+        <v>-7.78152451490928</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-12.19322591222138</v>
       </c>
       <c r="E38">
-        <v>-18.54530318372975</v>
+        <v>-28.77420215835952</v>
       </c>
       <c r="F38">
-        <v>-1.245221907953392</v>
+        <v>-3.04699887557818</v>
       </c>
       <c r="G38">
-        <v>0.8449295240466155</v>
+        <v>-7.863136083543393</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.91642868703638</v>
       </c>
       <c r="E39">
-        <v>-19.86731418621098</v>
+        <v>-27.37493086083343</v>
       </c>
       <c r="F39">
-        <v>-1.347401855456114</v>
+        <v>-3.370394337998509</v>
       </c>
       <c r="G39">
-        <v>0.8724434680234984</v>
+        <v>-8.075898224261275</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.65424173828658</v>
       </c>
       <c r="E40">
-        <v>-18.64644212221706</v>
+        <v>-27.64057114612337</v>
       </c>
       <c r="F40">
-        <v>-1.353173919518821</v>
+        <v>-3.46105749350011</v>
       </c>
       <c r="G40">
-        <v>0.7854456417969908</v>
+        <v>-7.892487380294572</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.41233612660886</v>
       </c>
       <c r="E41">
-        <v>-18.33257358874543</v>
+        <v>-27.01685989257292</v>
       </c>
       <c r="F41">
-        <v>-1.449362285597094</v>
+        <v>-3.291076502445651</v>
       </c>
       <c r="G41">
-        <v>0.6699175341130442</v>
+        <v>-8.03831029020839</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.19164045767064</v>
       </c>
       <c r="E42">
-        <v>-16.89773112788908</v>
+        <v>-26.61525670367669</v>
       </c>
       <c r="F42">
-        <v>-1.391646615174441</v>
+        <v>-3.286189134769134</v>
       </c>
       <c r="G42">
-        <v>1.046644374299948</v>
+        <v>-7.937563768357288</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.98862788313264</v>
       </c>
       <c r="E43">
-        <v>-18.06172555834666</v>
+        <v>-25.89243073952036</v>
       </c>
       <c r="F43">
-        <v>-1.653658396312522</v>
+        <v>-3.483806947483193</v>
       </c>
       <c r="G43">
-        <v>0.6415660221147258</v>
+        <v>-7.95790376015057</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.80971704560566</v>
       </c>
       <c r="E44">
-        <v>-17.72013823547408</v>
+        <v>-26.88331066561272</v>
       </c>
       <c r="F44">
-        <v>-1.18896830599668</v>
+        <v>-3.309977361475327</v>
       </c>
       <c r="G44">
-        <v>1.299358178585754</v>
+        <v>-8.463983546193418</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.6631262100616</v>
       </c>
       <c r="E45">
-        <v>-17.44664104778083</v>
+        <v>-25.37404726291432</v>
       </c>
       <c r="F45">
-        <v>-1.436955827005365</v>
+        <v>-3.324233564477507</v>
       </c>
       <c r="G45">
-        <v>0.6781707241424473</v>
+        <v>-8.235595630530177</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.550103233065</v>
       </c>
       <c r="E46">
-        <v>-16.80308149265476</v>
+        <v>-25.12987194442073</v>
       </c>
       <c r="F46">
-        <v>-1.496843476758158</v>
+        <v>-3.56823166807431</v>
       </c>
       <c r="G46">
-        <v>0.6844640712126018</v>
+        <v>-7.70398491728847</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.46895757715542</v>
       </c>
       <c r="E47">
-        <v>-15.78735382968232</v>
+        <v>-24.60494935134761</v>
       </c>
       <c r="F47">
-        <v>-1.602853795131425</v>
+        <v>-3.582413318010237</v>
       </c>
       <c r="G47">
-        <v>0.8772867961474521</v>
+        <v>-8.111695153177413</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.42917415167001</v>
       </c>
       <c r="E48">
-        <v>-14.98932349768061</v>
+        <v>-23.93516087476912</v>
       </c>
       <c r="F48">
-        <v>-1.570931828897143</v>
+        <v>-3.48604022600114</v>
       </c>
       <c r="G48">
-        <v>0.9937319249457769</v>
+        <v>-7.866565808722078</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.43045654210629</v>
       </c>
       <c r="E49">
-        <v>-15.51664165350378</v>
+        <v>-23.11120955754751</v>
       </c>
       <c r="F49">
-        <v>-1.992695920399914</v>
+        <v>-3.400276863687099</v>
       </c>
       <c r="G49">
-        <v>0.6179485902375651</v>
+        <v>-8.318425479922743</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.4624390220499</v>
       </c>
       <c r="E50">
-        <v>-13.98602196738521</v>
+        <v>-23.6849989136374</v>
       </c>
       <c r="F50">
-        <v>-1.480831134862044</v>
+        <v>-3.549916464798413</v>
       </c>
       <c r="G50">
-        <v>1.018369004849033</v>
+        <v>-7.765478300680432</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.52910587556581</v>
       </c>
       <c r="E51">
-        <v>-14.17810624936856</v>
+        <v>-22.80386202664692</v>
       </c>
       <c r="F51">
-        <v>-1.823832396971832</v>
+        <v>-3.560880735741867</v>
       </c>
       <c r="G51">
-        <v>0.6208386964933489</v>
+        <v>-8.052002706558815</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.6269686445609</v>
       </c>
       <c r="E52">
-        <v>-14.07905493739879</v>
+        <v>-22.44023914925301</v>
       </c>
       <c r="F52">
-        <v>-1.441675864466517</v>
+        <v>-3.601013479672698</v>
       </c>
       <c r="G52">
-        <v>0.5757887927949465</v>
+        <v>-8.194395891293947</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.74439529858478</v>
       </c>
       <c r="E53">
-        <v>-12.66587216772113</v>
+        <v>-22.69536884637116</v>
       </c>
       <c r="F53">
-        <v>-2.000458551331548</v>
+        <v>-3.468430791752428</v>
       </c>
       <c r="G53">
-        <v>0.5198107782714101</v>
+        <v>-8.571976852229984</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.87313631728194</v>
       </c>
       <c r="E54">
-        <v>-12.16047182609508</v>
+        <v>-21.06253697342546</v>
       </c>
       <c r="F54">
-        <v>-1.522047383355736</v>
+        <v>-3.757062159379471</v>
       </c>
       <c r="G54">
-        <v>0.2653159004854768</v>
+        <v>-8.106381727586884</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.0092921562465</v>
       </c>
       <c r="E55">
-        <v>-11.75546322474507</v>
+        <v>-21.54034532292277</v>
       </c>
       <c r="F55">
-        <v>-1.245469589806829</v>
+        <v>-3.501033675991811</v>
       </c>
       <c r="G55">
-        <v>-0.1207764730320254</v>
+        <v>-7.918130866041766</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.14318398198468</v>
       </c>
       <c r="E56">
-        <v>-11.18709445204237</v>
+        <v>-21.3543880662718</v>
       </c>
       <c r="F56">
-        <v>-1.628461945021569</v>
+        <v>-3.221129158953261</v>
       </c>
       <c r="G56">
-        <v>-0.7328069585137075</v>
+        <v>-8.731621289770258</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.26051392546978</v>
       </c>
       <c r="E57">
-        <v>-11.17877111681627</v>
+        <v>-20.24848490038461</v>
       </c>
       <c r="F57">
-        <v>-1.515542214141552</v>
+        <v>-3.202130552570054</v>
       </c>
       <c r="G57">
-        <v>0.170256895870844</v>
+        <v>-8.730800274476518</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.36054760309024</v>
       </c>
       <c r="E58">
-        <v>-10.95704344397871</v>
+        <v>-20.80610760426711</v>
       </c>
       <c r="F58">
-        <v>-1.556094111978199</v>
+        <v>-3.3822275663475</v>
       </c>
       <c r="G58">
-        <v>-0.05329431275952148</v>
+        <v>-8.557291272217777</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.43529479694401</v>
       </c>
       <c r="E59">
-        <v>-9.298711733895814</v>
+        <v>-20.54878612572926</v>
       </c>
       <c r="F59">
-        <v>-1.468895188955106</v>
+        <v>-3.454428069175505</v>
       </c>
       <c r="G59">
-        <v>-0.306461661784207</v>
+        <v>-8.531949046114654</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.47134557361288</v>
       </c>
       <c r="E60">
-        <v>-8.18952089587906</v>
+        <v>-20.60351726258596</v>
       </c>
       <c r="F60">
-        <v>-1.219865581753699</v>
+        <v>-3.613934354421564</v>
       </c>
       <c r="G60">
-        <v>-1.571325106519089</v>
+        <v>-8.768096880521947</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.46693747703515</v>
       </c>
       <c r="E61">
-        <v>-9.270028379531229</v>
+        <v>-20.17015135699993</v>
       </c>
       <c r="F61">
-        <v>-1.538941936535832</v>
+        <v>-3.254308586904992</v>
       </c>
       <c r="G61">
-        <v>-0.339312205170395</v>
+        <v>-8.840124419819871</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.41925913291946</v>
       </c>
       <c r="E62">
-        <v>-8.548615299265297</v>
+        <v>-19.72191847124671</v>
       </c>
       <c r="F62">
-        <v>-1.489032800517162</v>
+        <v>-3.607183160088748</v>
       </c>
       <c r="G62">
-        <v>-0.8979833176501041</v>
+        <v>-9.222131580141912</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.32156119036249</v>
       </c>
       <c r="E63">
-        <v>-8.927263653416652</v>
+        <v>-19.25535885118445</v>
       </c>
       <c r="F63">
-        <v>-1.747573722237513</v>
+        <v>-3.850827550804556</v>
       </c>
       <c r="G63">
-        <v>-0.7256462485122639</v>
+        <v>-9.244570457807091</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.17101047630105</v>
       </c>
       <c r="E64">
-        <v>-8.042014912027213</v>
+        <v>-19.55845414499183</v>
       </c>
       <c r="F64">
-        <v>-1.72046871245051</v>
+        <v>-3.062176223132272</v>
       </c>
       <c r="G64">
-        <v>-1.47034022538916</v>
+        <v>-9.070876064998151</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.97397476865229</v>
       </c>
       <c r="E65">
-        <v>-7.968748731057115</v>
+        <v>-18.49160001047279</v>
       </c>
       <c r="F65">
-        <v>-1.592494232392015</v>
+        <v>-3.466913222670499</v>
       </c>
       <c r="G65">
-        <v>-1.492855245601744</v>
+        <v>-9.420751070316026</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.73515679661419</v>
       </c>
       <c r="E66">
-        <v>-7.514379763023502</v>
+        <v>-17.97947035647134</v>
       </c>
       <c r="F66">
-        <v>-1.91515161945645</v>
+        <v>-3.662746731998928</v>
       </c>
       <c r="G66">
-        <v>-1.981713573749302</v>
+        <v>-8.631662677757504</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.4564984847885</v>
       </c>
       <c r="E67">
-        <v>-7.528762196471862</v>
+        <v>-19.33635966575964</v>
       </c>
       <c r="F67">
-        <v>-1.591591311922963</v>
+        <v>-3.60405027457136</v>
       </c>
       <c r="G67">
-        <v>-2.137329077368284</v>
+        <v>-9.227170230452684</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.15629670234178</v>
       </c>
       <c r="E68">
-        <v>-8.247308752690941</v>
+        <v>-18.59292461639441</v>
       </c>
       <c r="F68">
-        <v>-1.492244380937816</v>
+        <v>-3.489390972145464</v>
       </c>
       <c r="G68">
-        <v>-1.744999636054794</v>
+        <v>-9.451737776563604</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.848100056682185</v>
       </c>
       <c r="E69">
-        <v>-6.603948177677407</v>
+        <v>-19.19199191439511</v>
       </c>
       <c r="F69">
-        <v>-1.539600488621058</v>
+        <v>-3.568452013803455</v>
       </c>
       <c r="G69">
-        <v>-1.340755541345468</v>
+        <v>-9.724831299189164</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.540104173578552</v>
       </c>
       <c r="E70">
-        <v>-7.483875962107834</v>
+        <v>-18.59620323157596</v>
       </c>
       <c r="F70">
-        <v>-1.450027464621542</v>
+        <v>-3.630307036137896</v>
       </c>
       <c r="G70">
-        <v>-1.612889005764638</v>
+        <v>-8.861490680730327</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.248381422663474</v>
       </c>
       <c r="E71">
-        <v>-7.23555708989723</v>
+        <v>-17.98353692613022</v>
       </c>
       <c r="F71">
-        <v>-1.614808793488627</v>
+        <v>-3.582338764943986</v>
       </c>
       <c r="G71">
-        <v>-1.241674223900621</v>
+        <v>-9.389870301525704</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.987521965294489</v>
       </c>
       <c r="E72">
-        <v>-8.113388190862105</v>
+        <v>-18.45926670605802</v>
       </c>
       <c r="F72">
-        <v>-1.66853256139719</v>
+        <v>-3.893591189606677</v>
       </c>
       <c r="G72">
-        <v>-1.943516499317191</v>
+        <v>-9.946826551416072</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.764119124730593</v>
       </c>
       <c r="E73">
-        <v>-7.969441587580288</v>
+        <v>-19.44836694186536</v>
       </c>
       <c r="F73">
-        <v>-1.693130931423321</v>
+        <v>-4.060207352270965</v>
       </c>
       <c r="G73">
-        <v>-1.041204138770054</v>
+        <v>-9.493993579826862</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.58117254724327</v>
       </c>
       <c r="E74">
-        <v>-7.606321370801233</v>
+        <v>-18.82359602539712</v>
       </c>
       <c r="F74">
-        <v>-1.757014625527219</v>
+        <v>-3.872293035313299</v>
       </c>
       <c r="G74">
-        <v>-1.854234396668587</v>
+        <v>-9.839753577039422</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.44811377590937</v>
       </c>
       <c r="E75">
-        <v>-7.76951398861565</v>
+        <v>-18.94552065957964</v>
       </c>
       <c r="F75">
-        <v>-1.731936630774866</v>
+        <v>-3.698715272995885</v>
       </c>
       <c r="G75">
-        <v>-2.423687955969702</v>
+        <v>-9.50581222740206</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.365632593028209</v>
       </c>
       <c r="E76">
-        <v>-7.626110802214752</v>
+        <v>-19.54805224019621</v>
       </c>
       <c r="F76">
-        <v>-2.194001624791236</v>
+        <v>-3.823338178542654</v>
       </c>
       <c r="G76">
-        <v>-1.526013669723084</v>
+        <v>-9.072415468673912</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.324343127875569</v>
       </c>
       <c r="E77">
-        <v>-7.791762381415334</v>
+        <v>-19.74529898254831</v>
       </c>
       <c r="F77">
-        <v>-2.108293763093183</v>
+        <v>-3.90829222590416</v>
       </c>
       <c r="G77">
-        <v>-1.422817344172923</v>
+        <v>-9.559198084768347</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.327555522610597</v>
       </c>
       <c r="E78">
-        <v>-9.056270820947166</v>
+        <v>-20.4112473131683</v>
       </c>
       <c r="F78">
-        <v>-2.173505330143768</v>
+        <v>-4.240696183829934</v>
       </c>
       <c r="G78">
-        <v>-1.503753561517025</v>
+        <v>-8.847453967643817</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.371369602730075</v>
       </c>
       <c r="E79">
-        <v>-9.591835327938309</v>
+        <v>-20.38588785872534</v>
       </c>
       <c r="F79">
-        <v>-2.497411066884223</v>
+        <v>-4.17519220308616</v>
       </c>
       <c r="G79">
-        <v>-1.313033032999611</v>
+        <v>-8.660338623218671</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.44635892169736</v>
       </c>
       <c r="E80">
-        <v>-9.836871056493353</v>
+        <v>-20.81876468911855</v>
       </c>
       <c r="F80">
-        <v>-2.178743925599072</v>
+        <v>-4.058275599487636</v>
       </c>
       <c r="G80">
-        <v>-2.193518966806333</v>
+        <v>-9.299942642496942</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.549185820463395</v>
       </c>
       <c r="E81">
-        <v>-10.00951459956178</v>
+        <v>-21.51980869329799</v>
       </c>
       <c r="F81">
-        <v>-2.57481703047142</v>
+        <v>-4.454794366022689</v>
       </c>
       <c r="G81">
-        <v>-1.205880605530021</v>
+        <v>-8.935484684078578</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.679544398716027</v>
       </c>
       <c r="E82">
-        <v>-10.88584677563011</v>
+        <v>-22.04599020214523</v>
       </c>
       <c r="F82">
-        <v>-2.466518761331621</v>
+        <v>-4.175832531088525</v>
       </c>
       <c r="G82">
-        <v>-0.7377131870029074</v>
+        <v>-8.643057575503674</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.832298910708287</v>
       </c>
       <c r="E83">
-        <v>-12.1718201819583</v>
+        <v>-22.47631750167212</v>
       </c>
       <c r="F83">
-        <v>-3.008657890339605</v>
+        <v>-4.013557013614907</v>
       </c>
       <c r="G83">
-        <v>-0.8808512444843757</v>
+        <v>-8.674706390859107</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.999593903234091</v>
       </c>
       <c r="E84">
-        <v>-11.65650701072946</v>
+        <v>-23.56400261662645</v>
       </c>
       <c r="F84">
-        <v>-3.02526831350054</v>
+        <v>-4.252878983222907</v>
       </c>
       <c r="G84">
-        <v>-0.9916883091391751</v>
+        <v>-8.274428329705827</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.187436493446924</v>
       </c>
       <c r="E85">
-        <v>-14.23417328605753</v>
+        <v>-23.7046615477787</v>
       </c>
       <c r="F85">
-        <v>-2.99383508403391</v>
+        <v>-4.535208131649451</v>
       </c>
       <c r="G85">
-        <v>-1.235506677560959</v>
+        <v>-8.551494506978512</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.396441118148049</v>
       </c>
       <c r="E86">
-        <v>-15.04986013821514</v>
+        <v>-25.1502229066112</v>
       </c>
       <c r="F86">
-        <v>-3.211966587110896</v>
+        <v>-4.460686543358802</v>
       </c>
       <c r="G86">
-        <v>-0.3581061721968375</v>
+        <v>-8.355354615413312</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.621529555468879</v>
       </c>
       <c r="E87">
-        <v>-15.8730687856995</v>
+        <v>-25.58945318603717</v>
       </c>
       <c r="F87">
-        <v>-3.296030967881795</v>
+        <v>-4.42445043969074</v>
       </c>
       <c r="G87">
-        <v>0.08288497799839879</v>
+        <v>-8.022472640348516</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.871408351116379</v>
       </c>
       <c r="E88">
-        <v>-17.3561168523675</v>
+        <v>-27.44677057249111</v>
       </c>
       <c r="F88">
-        <v>-3.482491500047547</v>
+        <v>-4.727619655236914</v>
       </c>
       <c r="G88">
-        <v>-1.212680466067684</v>
+        <v>-8.800477326441559</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.15084135918055</v>
       </c>
       <c r="E89">
-        <v>-18.79035249770681</v>
+        <v>-28.31483375502144</v>
       </c>
       <c r="F89">
-        <v>-3.442648684707696</v>
+        <v>-5.08021009840151</v>
       </c>
       <c r="G89">
-        <v>-0.7341576610937302</v>
+        <v>-8.50571297271593</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-10.45767684542157</v>
       </c>
       <c r="E90">
-        <v>-21.24653792930512</v>
+        <v>-29.21507627385028</v>
       </c>
       <c r="F90">
-        <v>-4.159972608794526</v>
+        <v>-4.989302574516084</v>
       </c>
       <c r="G90">
-        <v>-0.8414458209304307</v>
+        <v>-8.707798604069662</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-10.79127331240317</v>
       </c>
       <c r="E91">
-        <v>-23.6533584657458</v>
+        <v>-31.56178584631315</v>
       </c>
       <c r="F91">
-        <v>-3.880286780750315</v>
+        <v>-4.995476396769149</v>
       </c>
       <c r="G91">
-        <v>0.0176804730569135</v>
+        <v>-7.996309398951656</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-11.15398630243651</v>
       </c>
       <c r="E92">
-        <v>-23.22714302061788</v>
+        <v>-32.31785986663379</v>
       </c>
       <c r="F92">
-        <v>-3.923216921400399</v>
+        <v>-5.438715913189497</v>
       </c>
       <c r="G92">
-        <v>-0.7841899358287356</v>
+        <v>-8.367113673168804</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-11.53838896573163</v>
       </c>
       <c r="E93">
-        <v>-25.56376768146567</v>
+        <v>-33.2582925922807</v>
       </c>
       <c r="F93">
-        <v>-4.681880520723937</v>
+        <v>-5.245442059135719</v>
       </c>
       <c r="G93">
-        <v>-0.3999547783587646</v>
+        <v>-8.930578455589377</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-11.92678307131863</v>
       </c>
       <c r="E94">
-        <v>-28.38294653257081</v>
+        <v>-35.88896918434256</v>
       </c>
       <c r="F94">
-        <v>-4.72922503126354</v>
+        <v>-5.582699421674496</v>
       </c>
       <c r="G94">
-        <v>-1.235834421569347</v>
+        <v>-8.878490332074485</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-12.31441482512956</v>
       </c>
       <c r="E95">
-        <v>-30.14937970992781</v>
+        <v>-37.59147615837028</v>
       </c>
       <c r="F95">
-        <v>-4.730251378475609</v>
+        <v>-5.321298975679681</v>
       </c>
       <c r="G95">
-        <v>-0.503419258097607</v>
+        <v>-8.781507900501534</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-12.68546369713391</v>
       </c>
       <c r="E96">
-        <v>-34.28832344040637</v>
+        <v>-39.70092992062328</v>
       </c>
       <c r="F96">
-        <v>-5.309867505521048</v>
+        <v>-5.775620391214681</v>
       </c>
       <c r="G96">
-        <v>-1.322729620884137</v>
+        <v>-8.204675135193384</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-13.0164926971299</v>
       </c>
       <c r="E97">
-        <v>-36.2123475132303</v>
+        <v>-41.67564346725207</v>
       </c>
       <c r="F97">
-        <v>-5.200343252625106</v>
+        <v>-5.863394201215317</v>
       </c>
       <c r="G97">
-        <v>-1.196803089661339</v>
+        <v>-9.576171251748191</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-13.29641537537407</v>
       </c>
       <c r="E98">
-        <v>-37.48477172532754</v>
+        <v>-43.84725053526034</v>
       </c>
       <c r="F98">
-        <v>-5.962703027299935</v>
+        <v>-5.975229599165069</v>
       </c>
       <c r="G98">
-        <v>-1.191065914241782</v>
+        <v>-9.490196384093318</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-13.51567064563445</v>
       </c>
       <c r="E99">
-        <v>-40.48067427458201</v>
+        <v>-45.05370393801384</v>
       </c>
       <c r="F99">
-        <v>-6.360113945527804</v>
+        <v>-5.759350427056296</v>
       </c>
       <c r="G99">
-        <v>-2.228064509508628</v>
+        <v>-9.561343318277794</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-13.66364152475464</v>
       </c>
       <c r="E100">
-        <v>-43.56051888227967</v>
+        <v>-48.1170128228725</v>
       </c>
       <c r="F100">
-        <v>-6.097416276180205</v>
+        <v>-6.044711400177087</v>
       </c>
       <c r="G100">
-        <v>-1.89600686028311</v>
+        <v>-9.806674606011025</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.73754167994253</v>
       </c>
       <c r="E101">
-        <v>-45.88096556973506</v>
+        <v>-49.52318211843077</v>
       </c>
       <c r="F101">
-        <v>-6.493493108705865</v>
+        <v>-6.467641004615596</v>
       </c>
       <c r="G101">
-        <v>-2.60184827471112</v>
+        <v>-9.763448812904763</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.75010161142826</v>
       </c>
       <c r="E102">
-        <v>-49.51687395413808</v>
+        <v>-51.88323483955725</v>
       </c>
       <c r="F102">
-        <v>-6.732253445214766</v>
+        <v>-6.270661448985395</v>
       </c>
       <c r="G102">
-        <v>-2.925172704804041</v>
+        <v>-10.37814428754556</v>
       </c>
     </row>
   </sheetData>
